--- a/ACCY122/Session/S05/ACCY122 L5 Workbook.xlsx
+++ b/ACCY122/Session/S05/ACCY122 L5 Workbook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\SIM-UOW-Mods\ACCY122\Session\S05\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/Desktop/SIM-UOW-Mods/ACCY122/Session/S05/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E57EA3-6B98-4052-BDC9-B09DD8E7DA47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA9F10B-AB3C-9944-B2C4-4D2EF92FD2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{49300C88-9C68-40D1-BFDB-69B44FEEA068}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18740" activeTab="7" xr2:uid="{49300C88-9C68-40D1-BFDB-69B44FEEA068}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="233">
   <si>
     <t>Balanced Day Adjustments</t>
   </si>
@@ -755,6 +755,21 @@
   </si>
   <si>
     <t>purchase account is an expense type account</t>
+  </si>
+  <si>
+    <t>Must manually verify the ending inventory</t>
+  </si>
+  <si>
+    <t>Jewellery Store</t>
+  </si>
+  <si>
+    <t>Each Transaction - COGS</t>
+  </si>
+  <si>
+    <t>Low Volume</t>
+  </si>
+  <si>
+    <t>Grocery Store</t>
   </si>
 </sst>
 </file>
@@ -1166,21 +1181,21 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1227,8 +1242,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1026232" y="661707"/>
-          <a:ext cx="5386393" cy="5936207"/>
+          <a:off x="1084719" y="653352"/>
+          <a:ext cx="5912775" cy="5849869"/>
           <a:chOff x="0" y="78429"/>
           <a:chExt cx="6059328" cy="3928254"/>
         </a:xfrm>
@@ -3170,7 +3185,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3154719-4B7A-4BD1-A273-F4DC249F84D4}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3180,27 +3195,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F923618A-53E6-4AA0-84BA-AB41705F9398}">
   <dimension ref="B1:O20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="37.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.2">
       <c r="G1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
       <c r="F3" t="s">
         <v>2</v>
       </c>
@@ -3217,7 +3232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
@@ -3235,7 +3250,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="2" t="s">
@@ -3249,8 +3264,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C6" s="73" t="s">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C6" s="78" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="1"/>
@@ -3277,8 +3292,8 @@
       </c>
       <c r="O6" s="7"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C7" s="73"/>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C7" s="78"/>
       <c r="D7" s="1"/>
       <c r="E7" s="2" t="s">
         <v>11</v>
@@ -3290,8 +3305,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C8" s="73"/>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C8" s="78"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
         <v>21</v>
@@ -3304,8 +3319,8 @@
       </c>
       <c r="O8" s="7"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C9" s="73"/>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C9" s="78"/>
       <c r="D9" s="1"/>
       <c r="E9" s="2" t="s">
         <v>11</v>
@@ -3313,8 +3328,8 @@
       <c r="M9" s="6"/>
       <c r="O9" s="7"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C10" s="73"/>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C10" s="78"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
         <v>23</v>
@@ -3342,7 +3357,7 @@
       </c>
       <c r="O10" s="7"/>
     </row>
-    <row r="11" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -3362,7 +3377,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="2" t="s">
@@ -3379,7 +3394,7 @@
       </c>
       <c r="O12" s="7"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>32</v>
       </c>
@@ -3396,7 +3411,7 @@
       <c r="M13" s="6"/>
       <c r="O13" s="7"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.2">
       <c r="F14" t="s">
         <v>42</v>
       </c>
@@ -3414,7 +3429,7 @@
       </c>
       <c r="O14" s="7"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
       <c r="M15" s="6" t="s">
         <v>36</v>
       </c>
@@ -3422,17 +3437,17 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
       <c r="M16" s="6" t="s">
         <v>37</v>
       </c>
       <c r="O16" s="7"/>
     </row>
-    <row r="17" spans="11:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="11:15" x14ac:dyDescent="0.2">
       <c r="M17" s="6"/>
       <c r="O17" s="7"/>
     </row>
-    <row r="18" spans="11:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="11:15" x14ac:dyDescent="0.2">
       <c r="K18">
         <v>4</v>
       </c>
@@ -3447,7 +3462,7 @@
       </c>
       <c r="O18" s="7"/>
     </row>
-    <row r="19" spans="11:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="11:15" x14ac:dyDescent="0.2">
       <c r="M19" s="6" t="s">
         <v>40</v>
       </c>
@@ -3455,7 +3470,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="11:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="11:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="M20" s="11" t="s">
         <v>41</v>
       </c>
@@ -3476,21 +3491,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED18275-5379-4236-A206-A963FAE5610E}">
   <dimension ref="B1:P85"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="11.85546875" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.5" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B2" s="3"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -3499,7 +3514,7 @@
       </c>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B3" s="6" t="s">
         <v>51</v>
       </c>
@@ -3513,14 +3528,14 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B4" s="6"/>
       <c r="E4" s="16" t="s">
         <v>59</v>
       </c>
       <c r="F4" s="7"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B5" s="6"/>
       <c r="C5" t="s">
         <v>65</v>
@@ -3530,7 +3545,7 @@
       </c>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B6" s="6" t="s">
         <v>71</v>
       </c>
@@ -3542,7 +3557,7 @@
       </c>
       <c r="F6" s="7"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B7" s="6"/>
       <c r="C7" t="s">
         <v>75</v>
@@ -3555,7 +3570,7 @@
       </c>
       <c r="F7" s="7"/>
     </row>
-    <row r="8" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11"/>
       <c r="C8" s="12" t="s">
         <v>76</v>
@@ -3568,8 +3583,23 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="H9" t="s">
+        <v>229</v>
+      </c>
+      <c r="M9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H10" t="s">
+        <v>230</v>
+      </c>
+      <c r="M10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>79</v>
       </c>
@@ -3580,8 +3610,14 @@
       <c r="E11" s="59" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="H11" t="s">
+        <v>231</v>
+      </c>
+      <c r="M11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B12" s="6"/>
       <c r="D12" t="s">
         <v>83</v>
@@ -3602,7 +3638,7 @@
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B13" s="6"/>
       <c r="C13" t="s">
         <v>86</v>
@@ -3638,7 +3674,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B14" s="6"/>
       <c r="C14" t="s">
         <v>94</v>
@@ -3663,7 +3699,7 @@
       </c>
       <c r="N14" s="16"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B15" s="6"/>
       <c r="D15" t="s">
         <v>98</v>
@@ -3685,7 +3721,7 @@
       </c>
       <c r="N15" s="16"/>
     </row>
-    <row r="16" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="6"/>
       <c r="C16" t="s">
         <v>100</v>
@@ -3706,7 +3742,7 @@
       <c r="N16" s="16"/>
       <c r="O16" s="7"/>
     </row>
-    <row r="17" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="11"/>
       <c r="C17" s="12" t="s">
         <v>102</v>
@@ -3744,8 +3780,11 @@
       <c r="O17" s="23">
         <v>25</v>
       </c>
-    </row>
-    <row r="18" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P17" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G18" s="11"/>
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
@@ -3762,7 +3801,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>109</v>
       </c>
@@ -3785,8 +3824,8 @@
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B22" s="3" t="s">
         <v>114</v>
       </c>
@@ -3810,7 +3849,7 @@
       </c>
       <c r="I22" s="5"/>
     </row>
-    <row r="23" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B23" s="6"/>
       <c r="C23" s="6" t="s">
         <v>116</v>
@@ -3826,7 +3865,7 @@
       </c>
       <c r="I23" s="7"/>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B24" s="3" t="s">
         <v>156</v>
       </c>
@@ -3846,7 +3885,7 @@
       </c>
       <c r="I24" s="5"/>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B25" s="6"/>
       <c r="D25" t="s">
         <v>155</v>
@@ -3862,18 +3901,18 @@
       </c>
       <c r="I25" s="7"/>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B26" s="6"/>
       <c r="H26" t="s">
         <v>153</v>
       </c>
       <c r="I26" s="7"/>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B27" s="6"/>
       <c r="I27" s="7"/>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B28" s="33" t="s">
         <v>115</v>
       </c>
@@ -3889,7 +3928,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B29" s="34" t="s">
         <v>145</v>
       </c>
@@ -3898,7 +3937,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B30" s="11"/>
       <c r="D30" s="32"/>
       <c r="E30" s="1"/>
@@ -3909,11 +3948,11 @@
         <v>146</v>
       </c>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B31" s="6"/>
       <c r="I31" s="7"/>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B32" s="6"/>
       <c r="D32" s="32"/>
       <c r="E32" s="32"/>
@@ -3924,11 +3963,11 @@
         <v>118</v>
       </c>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B33" s="6"/>
       <c r="I33" s="7"/>
     </row>
-    <row r="34" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B34" s="11"/>
       <c r="C34" s="12"/>
       <c r="D34" s="35"/>
@@ -3940,8 +3979,8 @@
         <v>147</v>
       </c>
     </row>
-    <row r="38" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:10" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B39" s="3" t="s">
         <v>120</v>
       </c>
@@ -3954,14 +3993,14 @@
       <c r="G39" s="4"/>
       <c r="H39" s="5"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B40" s="6"/>
       <c r="C40" t="s">
         <v>122</v>
       </c>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B41" s="11"/>
       <c r="C41" s="12" t="s">
         <v>124</v>
@@ -3974,8 +4013,8 @@
       <c r="G41" s="12"/>
       <c r="H41" s="13"/>
     </row>
-    <row r="42" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:10" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B43" s="3"/>
       <c r="C43" s="64" t="s">
         <v>60</v>
@@ -3994,7 +4033,7 @@
       </c>
       <c r="J43" s="5"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B44" s="6" t="s">
         <v>157</v>
       </c>
@@ -4006,7 +4045,7 @@
       </c>
       <c r="J44" s="7"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B45" s="6"/>
       <c r="C45">
         <v>-98</v>
@@ -4021,11 +4060,11 @@
         <v>160</v>
       </c>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B46" s="6"/>
       <c r="J46" s="7"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B47" s="6" t="s">
         <v>158</v>
       </c>
@@ -4037,7 +4076,7 @@
       </c>
       <c r="J47" s="7"/>
     </row>
-    <row r="48" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B48" s="11"/>
       <c r="C48" s="12">
         <v>-98</v>
@@ -4052,7 +4091,7 @@
       <c r="I48" s="12"/>
       <c r="J48" s="13"/>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B51" s="16"/>
       <c r="C51" s="16" t="s">
         <v>161</v>
@@ -4061,14 +4100,14 @@
       <c r="E51" s="16"/>
       <c r="F51" s="16"/>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B52" s="16"/>
       <c r="C52" s="16"/>
       <c r="D52" s="16"/>
       <c r="E52" s="16"/>
       <c r="F52" s="16"/>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.2">
       <c r="D54" t="s">
         <v>162</v>
       </c>
@@ -4076,7 +4115,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C55" s="36" t="s">
         <v>130</v>
       </c>
@@ -4099,7 +4138,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
         <v>166</v>
       </c>
@@ -4128,11 +4167,11 @@
       </c>
       <c r="L56" s="38"/>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.2">
       <c r="K57" s="38"/>
       <c r="L57" s="38"/>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B58" s="37" t="s">
         <v>168</v>
       </c>
@@ -4163,7 +4202,7 @@
       </c>
       <c r="L58" s="38"/>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B59" s="38"/>
       <c r="C59" s="38"/>
       <c r="D59" s="38"/>
@@ -4178,7 +4217,7 @@
       </c>
       <c r="L59" s="38"/>
     </row>
-    <row r="60" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B60" s="37"/>
       <c r="C60" s="38"/>
       <c r="D60" s="38"/>
@@ -4191,7 +4230,7 @@
       <c r="K60" s="38"/>
       <c r="L60" s="38"/>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B61" s="37" t="s">
         <v>171</v>
       </c>
@@ -4213,7 +4252,7 @@
       <c r="K61" s="38"/>
       <c r="L61" s="38"/>
     </row>
-    <row r="62" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B62" s="37"/>
       <c r="C62" s="42">
         <v>10</v>
@@ -4233,7 +4272,7 @@
       <c r="K62" s="38"/>
       <c r="L62" s="38"/>
     </row>
-    <row r="63" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B63" s="37"/>
       <c r="C63" s="37">
         <f>SUM(C61:C62)</f>
@@ -4264,7 +4303,7 @@
       </c>
       <c r="L63" s="38"/>
     </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B64" s="38"/>
       <c r="C64" s="37">
         <f>C63*50%</f>
@@ -4289,7 +4328,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="65" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B65" s="38"/>
       <c r="C65" s="38"/>
       <c r="D65" s="38"/>
@@ -4304,7 +4343,7 @@
       </c>
       <c r="L65" s="38"/>
     </row>
-    <row r="66" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B66" s="38"/>
       <c r="C66" s="38"/>
       <c r="D66" s="38"/>
@@ -4317,7 +4356,7 @@
       <c r="K66" s="38"/>
       <c r="L66" s="38"/>
     </row>
-    <row r="67" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B67" s="38"/>
       <c r="C67" s="38"/>
       <c r="D67" s="38"/>
@@ -4341,7 +4380,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="68" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B68" s="38"/>
       <c r="C68" s="38"/>
       <c r="D68" s="38"/>
@@ -4356,7 +4395,7 @@
       </c>
       <c r="L68" s="38"/>
     </row>
-    <row r="69" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B69" s="38"/>
       <c r="C69" s="38"/>
       <c r="D69" s="38"/>
@@ -4369,7 +4408,7 @@
       <c r="K69" s="38"/>
       <c r="L69" s="38"/>
     </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B70" s="38"/>
       <c r="C70" s="38"/>
       <c r="D70" s="38"/>
@@ -4386,7 +4425,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="71" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B71" s="38"/>
       <c r="C71" s="38"/>
       <c r="D71" s="38"/>
@@ -4401,14 +4440,14 @@
       </c>
       <c r="L71" s="38"/>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="K73" s="37"/>
       <c r="L73" s="37" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="75" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="G76" s="3"/>
       <c r="H76" s="49" t="s">
         <v>86</v>
@@ -4426,7 +4465,7 @@
       <c r="O76" s="49"/>
       <c r="P76" s="5"/>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="G77" s="6"/>
       <c r="H77" s="50" t="s">
         <v>179</v>
@@ -4444,7 +4483,7 @@
       <c r="O77" s="37"/>
       <c r="P77" s="51"/>
     </row>
-    <row r="78" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:16" x14ac:dyDescent="0.2">
       <c r="G78" s="6"/>
       <c r="H78" s="37"/>
       <c r="I78" s="37"/>
@@ -4456,7 +4495,7 @@
       <c r="O78" s="37"/>
       <c r="P78" s="51"/>
     </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="G79" s="6"/>
       <c r="H79" s="37"/>
       <c r="I79" s="37" t="s">
@@ -4484,7 +4523,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="G80" s="6"/>
       <c r="H80" s="37"/>
       <c r="I80" s="52" t="s">
@@ -4512,7 +4551,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="81" spans="7:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G81" s="6"/>
       <c r="H81" s="54" t="s">
         <v>78</v>
@@ -4542,7 +4581,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="7:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G82" s="6" t="s">
         <v>189</v>
       </c>
@@ -4574,7 +4613,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="83" spans="7:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="7:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G83" s="55" t="s">
         <v>191</v>
       </c>
@@ -4614,7 +4653,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="7:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="7:16" x14ac:dyDescent="0.2">
       <c r="H84" s="37" t="s">
         <v>53</v>
       </c>
@@ -4625,7 +4664,7 @@
       <c r="M84" s="37"/>
       <c r="N84" s="37"/>
     </row>
-    <row r="85" spans="7:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="7:16" x14ac:dyDescent="0.2">
       <c r="H85" s="37" t="s">
         <v>193</v>
       </c>
@@ -4640,16 +4679,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BB63E4-B13E-4175-A150-ABC62D398D37}">
   <dimension ref="A1:T43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="6" width="3.85546875" customWidth="1"/>
-    <col min="10" max="10" width="17.85546875" customWidth="1"/>
-    <col min="13" max="13" width="26.5703125" customWidth="1"/>
-    <col min="16" max="16" width="3.42578125" customWidth="1"/>
-    <col min="18" max="18" width="23.85546875" customWidth="1"/>
+    <col min="6" max="6" width="3.83203125" customWidth="1"/>
+    <col min="10" max="10" width="17.83203125" customWidth="1"/>
+    <col min="13" max="13" width="26.5" customWidth="1"/>
+    <col min="16" max="16" width="3.5" customWidth="1"/>
+    <col min="18" max="18" width="23.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="61" t="s">
         <v>45</v>
       </c>
@@ -4665,7 +4704,7 @@
       <c r="I1" s="4"/>
       <c r="J1" s="5"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="6"/>
       <c r="B2" s="1" t="s">
         <v>48</v>
@@ -4681,7 +4720,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="6"/>
       <c r="C3" t="s">
         <v>55</v>
@@ -4696,20 +4735,20 @@
         <v>58</v>
       </c>
       <c r="J3" s="7"/>
-      <c r="L3" s="76" t="s">
+      <c r="L3" s="77" t="s">
         <v>204</v>
       </c>
-      <c r="M3" s="76"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="Q3" s="76" t="s">
+      <c r="M3" s="77"/>
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="Q3" s="77" t="s">
         <v>206</v>
       </c>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="6"/>
       <c r="B4" t="s">
         <v>60</v>
@@ -4754,7 +4793,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" t="s">
         <v>67</v>
@@ -4772,7 +4811,7 @@
       <c r="L5">
         <v>1</v>
       </c>
-      <c r="M5" s="75" t="s">
+      <c r="M5" s="74" t="s">
         <v>68</v>
       </c>
       <c r="N5">
@@ -4788,7 +4827,7 @@
         <v>27190</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
         <v>73</v>
       </c>
@@ -4808,20 +4847,20 @@
         <v>74</v>
       </c>
       <c r="J6" s="7"/>
-      <c r="M6" s="74" t="s">
+      <c r="M6" s="73" t="s">
         <v>70</v>
       </c>
       <c r="O6">
         <v>27190</v>
       </c>
-      <c r="R6" s="74" t="s">
+      <c r="R6" s="73" t="s">
         <v>70</v>
       </c>
       <c r="T6">
         <v>27190</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>1</v>
       </c>
@@ -4832,21 +4871,21 @@
         <v>27190</v>
       </c>
       <c r="J7" s="7"/>
-      <c r="L7" s="77"/>
-      <c r="M7" s="77" t="s">
+      <c r="L7" s="75"/>
+      <c r="M7" s="75" t="s">
         <v>207</v>
       </c>
-      <c r="N7" s="77"/>
-      <c r="O7" s="77"/>
-      <c r="P7" s="77"/>
-      <c r="Q7" s="77"/>
-      <c r="R7" s="77" t="s">
+      <c r="N7" s="75"/>
+      <c r="O7" s="75"/>
+      <c r="P7" s="75"/>
+      <c r="Q7" s="75"/>
+      <c r="R7" s="75" t="s">
         <v>207</v>
       </c>
-      <c r="S7" s="77"/>
-      <c r="T7" s="77"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="S7" s="75"/>
+      <c r="T7" s="75"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>2</v>
       </c>
@@ -4869,14 +4908,14 @@
       <c r="Q8">
         <v>2</v>
       </c>
-      <c r="R8" s="75" t="s">
+      <c r="R8" s="74" t="s">
         <v>70</v>
       </c>
       <c r="S8">
         <v>1590</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>3</v>
       </c>
@@ -4894,7 +4933,7 @@
       <c r="J9" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="M9" s="74" t="s">
+      <c r="M9" s="73" t="s">
         <v>68</v>
       </c>
       <c r="O9">
@@ -4907,7 +4946,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>4</v>
       </c>
@@ -4924,21 +4963,21 @@
       <c r="J10" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="L10" s="77"/>
-      <c r="M10" s="77" t="s">
+      <c r="L10" s="75"/>
+      <c r="M10" s="75" t="s">
         <v>209</v>
       </c>
-      <c r="N10" s="77"/>
-      <c r="O10" s="77"/>
-      <c r="P10" s="77"/>
-      <c r="Q10" s="77"/>
-      <c r="R10" s="77" t="s">
+      <c r="N10" s="75"/>
+      <c r="O10" s="75"/>
+      <c r="P10" s="75"/>
+      <c r="Q10" s="75"/>
+      <c r="R10" s="75" t="s">
         <v>209</v>
       </c>
-      <c r="S10" s="77"/>
-      <c r="T10" s="77"/>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="S10" s="75"/>
+      <c r="T10" s="75"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
       <c r="C11">
         <v>-24900</v>
@@ -4952,7 +4991,7 @@
       <c r="L11">
         <v>3</v>
       </c>
-      <c r="M11" s="75" t="s">
+      <c r="M11" s="74" t="s">
         <v>70</v>
       </c>
       <c r="N11">
@@ -4961,14 +5000,14 @@
       <c r="Q11">
         <v>3</v>
       </c>
-      <c r="R11" s="75" t="s">
+      <c r="R11" s="74" t="s">
         <v>70</v>
       </c>
       <c r="S11">
         <v>25600</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>5</v>
       </c>
@@ -4981,20 +5020,20 @@
       <c r="J12" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="M12" s="74" t="s">
+      <c r="M12" s="73" t="s">
         <v>211</v>
       </c>
       <c r="O12">
         <v>512</v>
       </c>
-      <c r="R12" s="74" t="s">
+      <c r="R12" s="73" t="s">
         <v>211</v>
       </c>
       <c r="T12">
         <v>512</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="C13" s="1">
         <v>1010</v>
@@ -5005,20 +5044,20 @@
       <c r="J13" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="M13" s="74" t="s">
+      <c r="M13" s="73" t="s">
         <v>60</v>
       </c>
       <c r="O13">
         <v>25088</v>
       </c>
-      <c r="R13" s="74" t="s">
+      <c r="R13" s="73" t="s">
         <v>60</v>
       </c>
       <c r="T13">
         <v>25088</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>6</v>
       </c>
@@ -5031,21 +5070,21 @@
       <c r="J14" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="L14" s="77"/>
-      <c r="M14" s="77" t="s">
+      <c r="L14" s="75"/>
+      <c r="M14" s="75" t="s">
         <v>212</v>
       </c>
-      <c r="N14" s="77"/>
-      <c r="O14" s="77"/>
-      <c r="P14" s="77"/>
-      <c r="Q14" s="77"/>
-      <c r="R14" s="77" t="s">
+      <c r="N14" s="75"/>
+      <c r="O14" s="75"/>
+      <c r="P14" s="75"/>
+      <c r="Q14" s="75"/>
+      <c r="R14" s="75" t="s">
         <v>212</v>
       </c>
-      <c r="S14" s="77"/>
-      <c r="T14" s="77"/>
-    </row>
-    <row r="15" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S14" s="75"/>
+      <c r="T14" s="75"/>
+    </row>
+    <row r="15" spans="1:20" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
         <v>73</v>
       </c>
@@ -5080,7 +5119,7 @@
         <v>23000</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="I16" s="6">
         <f>I11+I13</f>
         <v>-23890</v>
@@ -5088,20 +5127,20 @@
       <c r="J16" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="M16" s="74" t="s">
+      <c r="M16" s="73" t="s">
         <v>69</v>
       </c>
       <c r="N16">
         <v>26820</v>
       </c>
-      <c r="R16" s="74" t="s">
+      <c r="R16" s="73" t="s">
         <v>69</v>
       </c>
       <c r="S16">
         <v>26820</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="I17" s="6">
         <f>I14</f>
         <v>-4280</v>
@@ -5109,20 +5148,20 @@
       <c r="J17" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="M17" s="74" t="s">
+      <c r="M17" s="73" t="s">
         <v>78</v>
       </c>
       <c r="O17">
         <v>49820</v>
       </c>
-      <c r="R17" s="74" t="s">
+      <c r="R17" s="73" t="s">
         <v>78</v>
       </c>
       <c r="T17">
         <v>49820</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="I18" s="65">
         <f>SUM(I16:I17)</f>
         <v>-28170</v>
@@ -5133,21 +5172,21 @@
       <c r="K18" t="s">
         <v>108</v>
       </c>
-      <c r="L18" s="77"/>
-      <c r="M18" s="78" t="s">
+      <c r="L18" s="75"/>
+      <c r="M18" s="76" t="s">
         <v>213</v>
       </c>
-      <c r="N18" s="77"/>
-      <c r="O18" s="77"/>
-      <c r="P18" s="77"/>
-      <c r="Q18" s="77"/>
-      <c r="R18" s="78" t="s">
+      <c r="N18" s="75"/>
+      <c r="O18" s="75"/>
+      <c r="P18" s="75"/>
+      <c r="Q18" s="75"/>
+      <c r="R18" s="76" t="s">
         <v>213</v>
       </c>
-      <c r="S18" s="77"/>
-      <c r="T18" s="77"/>
-    </row>
-    <row r="19" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S18" s="75"/>
+      <c r="T18" s="75"/>
+    </row>
+    <row r="19" spans="1:20" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="L19">
         <v>4</v>
       </c>
@@ -5158,7 +5197,7 @@
         <v>24900</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" s="3"/>
       <c r="B20" s="15" t="s">
         <v>48</v>
@@ -5177,14 +5216,14 @@
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="5"/>
-      <c r="M20" s="74" t="s">
+      <c r="M20" s="73" t="s">
         <v>68</v>
       </c>
       <c r="O20">
         <v>24900</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" s="62" t="s">
         <v>113</v>
       </c>
@@ -5201,19 +5240,19 @@
         <v>58</v>
       </c>
       <c r="J21" s="7"/>
-      <c r="L21" s="77"/>
-      <c r="M21" s="77" t="s">
+      <c r="L21" s="75"/>
+      <c r="M21" s="75" t="s">
         <v>214</v>
       </c>
-      <c r="N21" s="77"/>
-      <c r="O21" s="77"/>
-      <c r="P21" s="77"/>
-      <c r="Q21" s="77"/>
-      <c r="R21" s="77"/>
-      <c r="S21" s="77"/>
-      <c r="T21" s="77"/>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="N21" s="75"/>
+      <c r="O21" s="75"/>
+      <c r="P21" s="75"/>
+      <c r="Q21" s="75"/>
+      <c r="R21" s="75"/>
+      <c r="S21" s="75"/>
+      <c r="T21" s="75"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" s="6"/>
       <c r="B22" t="s">
         <v>60</v>
@@ -5252,7 +5291,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" s="6"/>
       <c r="B23" t="s">
         <v>67</v>
@@ -5267,20 +5306,20 @@
         <v>70</v>
       </c>
       <c r="J23" s="7"/>
-      <c r="M23" s="74" t="s">
+      <c r="M23" s="73" t="s">
         <v>69</v>
       </c>
       <c r="O23">
         <v>2020</v>
       </c>
-      <c r="R23" s="74" t="s">
+      <c r="R23" s="73" t="s">
         <v>69</v>
       </c>
       <c r="T23">
         <v>2020</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
         <v>73</v>
       </c>
@@ -5300,21 +5339,21 @@
         <v>74</v>
       </c>
       <c r="J24" s="7"/>
-      <c r="L24" s="77"/>
-      <c r="M24" s="77" t="s">
+      <c r="L24" s="75"/>
+      <c r="M24" s="75" t="s">
         <v>215</v>
       </c>
-      <c r="N24" s="77"/>
-      <c r="O24" s="77"/>
-      <c r="P24" s="77"/>
-      <c r="Q24" s="77"/>
-      <c r="R24" s="77" t="s">
+      <c r="N24" s="75"/>
+      <c r="O24" s="75"/>
+      <c r="P24" s="75"/>
+      <c r="Q24" s="75"/>
+      <c r="R24" s="75" t="s">
         <v>215</v>
       </c>
-      <c r="S24" s="77"/>
-      <c r="T24" s="77"/>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="S24" s="75"/>
+      <c r="T24" s="75"/>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" s="18">
         <v>0</v>
       </c>
@@ -5328,7 +5367,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" s="6">
         <v>1</v>
       </c>
@@ -5342,7 +5381,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>2</v>
       </c>
@@ -5364,9 +5403,9 @@
       <c r="N27" t="s">
         <v>225</v>
       </c>
-      <c r="R27" s="75"/>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="R27" s="74"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>3</v>
       </c>
@@ -5390,7 +5429,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>4</v>
       </c>
@@ -5411,7 +5450,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" s="6"/>
       <c r="J30" s="7" t="s">
         <v>123</v>
@@ -5420,7 +5459,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>5</v>
       </c>
@@ -5437,13 +5476,13 @@
         <v>223</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" s="6"/>
       <c r="J32" s="7" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <v>6</v>
       </c>
@@ -5457,7 +5496,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="18" t="s">
         <v>73</v>
       </c>
@@ -5467,11 +5506,11 @@
       </c>
       <c r="J34" s="7"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="6"/>
       <c r="J35" s="7"/>
     </row>
-    <row r="36" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
@@ -5491,27 +5530,27 @@
         <v>108</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K39" s="16" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K40" s="16" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K41" s="16" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K42" s="16" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K43" s="16" t="s">
         <v>226</v>
       </c>
@@ -5530,22 +5569,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E563E95-2F44-428E-8B27-57253C67817A}">
   <dimension ref="A1:O83"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" customWidth="1"/>
-    <col min="7" max="7" width="4.140625" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" customWidth="1"/>
+    <col min="3" max="3" width="4.5" customWidth="1"/>
+    <col min="6" max="6" width="9.5" customWidth="1"/>
+    <col min="7" max="7" width="4.1640625" customWidth="1"/>
+    <col min="11" max="11" width="4.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="30"/>
       <c r="B2" s="30"/>
       <c r="D2" s="30"/>
@@ -5564,7 +5603,7 @@
       </c>
       <c r="N2" s="30"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="30" t="s">
         <v>127</v>
       </c>
@@ -5599,7 +5638,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="31">
         <v>37104</v>
       </c>
@@ -5623,7 +5662,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="30"/>
       <c r="B5" s="30"/>
       <c r="D5" s="30"/>
@@ -5636,7 +5675,7 @@
       <c r="M5" s="30"/>
       <c r="N5" s="30"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="30">
         <v>12</v>
       </c>
@@ -5672,7 +5711,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="30"/>
       <c r="B7" s="30"/>
       <c r="D7" s="30"/>
@@ -5697,7 +5736,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="30"/>
       <c r="B8" s="30"/>
       <c r="D8" s="30"/>
@@ -5710,7 +5749,7 @@
       <c r="M8" s="30"/>
       <c r="N8" s="30"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="30">
         <v>15</v>
       </c>
@@ -5744,7 +5783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="30"/>
       <c r="B10" s="30"/>
       <c r="D10" s="30"/>
@@ -5772,7 +5811,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="30"/>
       <c r="B11" s="30"/>
       <c r="D11" s="30"/>
@@ -5785,7 +5824,7 @@
       <c r="M11" s="30"/>
       <c r="N11" s="30"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="30">
         <v>21</v>
       </c>
@@ -5821,7 +5860,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="30"/>
       <c r="B13" s="30"/>
       <c r="D13" s="30"/>
@@ -5846,7 +5885,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="30"/>
       <c r="B14" s="30"/>
       <c r="D14" s="30"/>
@@ -5859,7 +5898,7 @@
       <c r="M14" s="30"/>
       <c r="N14" s="30"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="30">
         <v>22</v>
       </c>
@@ -5893,7 +5932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="30"/>
       <c r="B16" s="30"/>
       <c r="D16" s="30"/>
@@ -5923,7 +5962,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="30"/>
       <c r="B17" s="30"/>
       <c r="D17" s="30"/>
@@ -5936,7 +5975,7 @@
       <c r="M17" s="30"/>
       <c r="N17" s="30"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="30">
         <v>28</v>
       </c>
@@ -5969,7 +6008,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="30"/>
       <c r="B19" s="30"/>
       <c r="D19" s="30"/>
@@ -5981,7 +6020,7 @@
       <c r="M19" s="30"/>
       <c r="N19" s="30"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="J20" s="70">
         <f>SUM(J9:J18)</f>
         <v>2915</v>
@@ -5997,12 +6036,12 @@
         <v>196</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="30"/>
       <c r="B23" s="30"/>
       <c r="D23" s="30"/>
@@ -6021,7 +6060,7 @@
       </c>
       <c r="N23" s="30"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="30" t="s">
         <v>127</v>
       </c>
@@ -6056,7 +6095,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="31">
         <v>37104</v>
       </c>
@@ -6080,7 +6119,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="30"/>
       <c r="B26" s="30"/>
       <c r="D26" s="30"/>
@@ -6093,7 +6132,7 @@
       <c r="M26" s="30"/>
       <c r="N26" s="30"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="30">
         <v>12</v>
       </c>
@@ -6129,7 +6168,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="30"/>
       <c r="B28" s="30"/>
       <c r="D28" s="30"/>
@@ -6154,7 +6193,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="30"/>
       <c r="B29" s="30"/>
       <c r="D29" s="30"/>
@@ -6167,7 +6206,7 @@
       <c r="M29" s="30"/>
       <c r="N29" s="30"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" s="30">
         <v>15</v>
       </c>
@@ -6202,7 +6241,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" s="30"/>
       <c r="B31" s="30"/>
       <c r="D31" s="30"/>
@@ -6233,7 +6272,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" s="30"/>
       <c r="B32" s="30"/>
       <c r="D32" s="30"/>
@@ -6246,7 +6285,7 @@
       <c r="M32" s="71"/>
       <c r="N32" s="71"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" s="30">
         <v>21</v>
       </c>
@@ -6282,7 +6321,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" s="30"/>
       <c r="B34" s="30"/>
       <c r="D34" s="30"/>
@@ -6307,7 +6346,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="30"/>
       <c r="B35" s="30"/>
       <c r="D35" s="30"/>
@@ -6332,7 +6371,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" s="30"/>
       <c r="B36" s="30"/>
       <c r="D36" s="30"/>
@@ -6345,7 +6384,7 @@
       <c r="M36" s="72"/>
       <c r="N36" s="72"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" s="30">
         <v>22</v>
       </c>
@@ -6384,7 +6423,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" s="30"/>
       <c r="B38" s="30"/>
       <c r="D38" s="30"/>
@@ -6419,7 +6458,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" s="30"/>
       <c r="B39" s="30"/>
       <c r="D39" s="30"/>
@@ -6454,7 +6493,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" s="30"/>
       <c r="B40" s="30"/>
       <c r="D40" s="30"/>
@@ -6467,7 +6506,7 @@
       <c r="M40" s="72"/>
       <c r="N40" s="72"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" s="30">
         <v>28</v>
       </c>
@@ -6503,7 +6542,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" s="30"/>
       <c r="B42" s="30"/>
       <c r="D42" s="30"/>
@@ -6535,7 +6574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="G43" t="s">
         <v>194</v>
       </c>
@@ -6562,7 +6601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="J45" s="1">
         <f>SUM(J30:J43)</f>
         <v>2990</v>
@@ -6578,12 +6617,12 @@
         <v>196</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" s="30"/>
       <c r="B47" s="30"/>
       <c r="D47" s="30"/>
@@ -6602,7 +6641,7 @@
       </c>
       <c r="N47" s="30"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" s="30" t="s">
         <v>127</v>
       </c>
@@ -6637,7 +6676,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="31">
         <v>37104</v>
       </c>
@@ -6661,7 +6700,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="30"/>
       <c r="B50" s="30"/>
       <c r="D50" s="30"/>
@@ -6674,7 +6713,7 @@
       <c r="M50" s="30"/>
       <c r="N50" s="30"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="30">
         <v>12</v>
       </c>
@@ -6696,7 +6735,7 @@
       <c r="M51" s="30"/>
       <c r="N51" s="30"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" s="30"/>
       <c r="B52" s="30"/>
       <c r="D52" s="30"/>
@@ -6709,7 +6748,7 @@
       <c r="M52" s="30"/>
       <c r="N52" s="30"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" s="30">
         <v>15</v>
       </c>
@@ -6726,7 +6765,7 @@
       <c r="M53" s="30"/>
       <c r="N53" s="30"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" s="30"/>
       <c r="B54" s="30"/>
       <c r="D54" s="30"/>
@@ -6739,7 +6778,7 @@
       <c r="M54" s="30"/>
       <c r="N54" s="30"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" s="30"/>
       <c r="B55" s="30"/>
       <c r="D55" s="30"/>
@@ -6752,7 +6791,7 @@
       <c r="M55" s="30"/>
       <c r="N55" s="30"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" s="30">
         <v>21</v>
       </c>
@@ -6774,7 +6813,7 @@
       <c r="M56" s="30"/>
       <c r="N56" s="30"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" s="30"/>
       <c r="B57" s="30"/>
       <c r="D57" s="30"/>
@@ -6787,7 +6826,7 @@
       <c r="M57" s="30"/>
       <c r="N57" s="30"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" s="30"/>
       <c r="B58" s="30"/>
       <c r="D58" s="30"/>
@@ -6800,7 +6839,7 @@
       <c r="M58" s="30"/>
       <c r="N58" s="30"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" s="30"/>
       <c r="B59" s="30"/>
       <c r="D59" s="30"/>
@@ -6813,7 +6852,7 @@
       <c r="M59" s="30"/>
       <c r="N59" s="30"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60" s="30">
         <v>22</v>
       </c>
@@ -6830,7 +6869,7 @@
       <c r="M60" s="30"/>
       <c r="N60" s="30"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" s="30"/>
       <c r="B61" s="30"/>
       <c r="D61" s="30"/>
@@ -6843,7 +6882,7 @@
       <c r="M61" s="30"/>
       <c r="N61" s="30"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62" s="30">
         <v>28</v>
       </c>
@@ -6860,7 +6899,7 @@
       <c r="M62" s="30"/>
       <c r="N62" s="30"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" s="30"/>
       <c r="B63" s="30"/>
       <c r="D63" s="30"/>
@@ -6873,12 +6912,12 @@
       <c r="M63" s="30"/>
       <c r="N63" s="30"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67" s="30"/>
       <c r="B67" s="30"/>
       <c r="D67" s="30"/>
@@ -6897,7 +6936,7 @@
       </c>
       <c r="N67" s="30"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" s="30" t="s">
         <v>127</v>
       </c>
@@ -6932,7 +6971,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69" s="31">
         <v>37104</v>
       </c>
@@ -6956,7 +6995,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70" s="30"/>
       <c r="B70" s="30"/>
       <c r="D70" s="30"/>
@@ -6969,7 +7008,7 @@
       <c r="M70" s="30"/>
       <c r="N70" s="30"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71" s="30">
         <v>12</v>
       </c>
@@ -6991,7 +7030,7 @@
       <c r="M71" s="30"/>
       <c r="N71" s="30"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72" s="30"/>
       <c r="B72" s="30"/>
       <c r="D72" s="30"/>
@@ -7004,7 +7043,7 @@
       <c r="M72" s="30"/>
       <c r="N72" s="30"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73" s="30">
         <v>15</v>
       </c>
@@ -7021,7 +7060,7 @@
       <c r="M73" s="30"/>
       <c r="N73" s="30"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74" s="30"/>
       <c r="B74" s="30"/>
       <c r="D74" s="30"/>
@@ -7034,7 +7073,7 @@
       <c r="M74" s="30"/>
       <c r="N74" s="30"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75" s="30"/>
       <c r="B75" s="30"/>
       <c r="D75" s="30"/>
@@ -7047,7 +7086,7 @@
       <c r="M75" s="30"/>
       <c r="N75" s="30"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76" s="30">
         <v>21</v>
       </c>
@@ -7069,7 +7108,7 @@
       <c r="M76" s="30"/>
       <c r="N76" s="30"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77" s="30"/>
       <c r="B77" s="30"/>
       <c r="D77" s="30"/>
@@ -7082,7 +7121,7 @@
       <c r="M77" s="30"/>
       <c r="N77" s="30"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78" s="30"/>
       <c r="B78" s="30"/>
       <c r="D78" s="30"/>
@@ -7095,7 +7134,7 @@
       <c r="M78" s="30"/>
       <c r="N78" s="30"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79" s="30"/>
       <c r="B79" s="30"/>
       <c r="D79" s="30"/>
@@ -7108,7 +7147,7 @@
       <c r="M79" s="30"/>
       <c r="N79" s="30"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80" s="30">
         <v>22</v>
       </c>
@@ -7125,7 +7164,7 @@
       <c r="M80" s="30"/>
       <c r="N80" s="30"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81" s="30"/>
       <c r="B81" s="30"/>
       <c r="D81" s="30"/>
@@ -7138,7 +7177,7 @@
       <c r="M81" s="30"/>
       <c r="N81" s="30"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82" s="30">
         <v>28</v>
       </c>
@@ -7155,7 +7194,7 @@
       <c r="M82" s="30"/>
       <c r="N82" s="30"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83" s="30"/>
       <c r="B83" s="30"/>
       <c r="D83" s="30"/>
@@ -7178,7 +7217,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5CAAE00-9AF3-49EE-BA1C-A5290505E222}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7190,13 +7229,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:L36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="7" max="7" width="3.85546875" customWidth="1"/>
-    <col min="11" max="11" width="17.85546875" customWidth="1"/>
+    <col min="7" max="7" width="3.83203125" customWidth="1"/>
+    <col min="11" max="11" width="17.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B1" s="3" t="s">
         <v>45</v>
       </c>
@@ -7212,7 +7251,7 @@
       <c r="J1" s="4"/>
       <c r="K1" s="5"/>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B2" s="6"/>
       <c r="C2" s="1" t="s">
         <v>48</v>
@@ -7225,7 +7264,7 @@
       </c>
       <c r="K2" s="7"/>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="6"/>
       <c r="D3" t="s">
         <v>55</v>
@@ -7241,7 +7280,7 @@
       </c>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="6"/>
       <c r="C4" t="s">
         <v>60</v>
@@ -7262,7 +7301,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="6"/>
       <c r="C5" t="s">
         <v>67</v>
@@ -7278,7 +7317,7 @@
       </c>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="18" t="s">
         <v>73</v>
       </c>
@@ -7299,7 +7338,7 @@
       </c>
       <c r="K6" s="7"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="6">
         <v>1</v>
       </c>
@@ -7314,7 +7353,7 @@
       </c>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="6">
         <v>2</v>
       </c>
@@ -7329,7 +7368,7 @@
       </c>
       <c r="K8" s="7"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="6">
         <v>3</v>
       </c>
@@ -7351,7 +7390,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="6">
         <v>4</v>
       </c>
@@ -7372,7 +7411,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="6"/>
       <c r="D11" s="19">
         <v>-24900</v>
@@ -7387,7 +7426,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="6">
         <v>5</v>
       </c>
@@ -7404,7 +7443,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="6"/>
       <c r="D13" s="1">
         <v>1010</v>
@@ -7419,7 +7458,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" s="6">
         <v>6</v>
       </c>
@@ -7437,7 +7476,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="20" t="s">
         <v>73</v>
       </c>
@@ -7454,7 +7493,7 @@
       <c r="J15" s="12"/>
       <c r="K15" s="13"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="J16" s="6">
         <f>J11+J13</f>
         <v>-23890</v>
@@ -7463,7 +7502,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J17" s="6">
         <f>J14</f>
         <v>-4280</v>
@@ -7472,7 +7511,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="J18" s="25">
         <f>SUM(J16:J17)</f>
         <v>-28170</v>
@@ -7484,8 +7523,8 @@
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" s="3"/>
       <c r="C20" s="15" t="s">
         <v>48</v>
@@ -7505,7 +7544,7 @@
       <c r="J20" s="4"/>
       <c r="K20" s="5"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B21" s="6" t="s">
         <v>113</v>
       </c>
@@ -7523,7 +7562,7 @@
       </c>
       <c r="K21" s="7"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22" s="6"/>
       <c r="C22" t="s">
         <v>60</v>
@@ -7544,7 +7583,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B23" s="6"/>
       <c r="C23" t="s">
         <v>67</v>
@@ -7560,7 +7599,7 @@
       </c>
       <c r="K23" s="7"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B24" s="18" t="s">
         <v>73</v>
       </c>
@@ -7581,7 +7620,7 @@
       </c>
       <c r="K24" s="7"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B25" s="18">
         <v>0</v>
       </c>
@@ -7595,7 +7634,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="6">
         <v>1</v>
       </c>
@@ -7612,7 +7651,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="6">
         <v>2</v>
       </c>
@@ -7629,7 +7668,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B28" s="6">
         <v>3</v>
       </c>
@@ -7651,7 +7690,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B29" s="6">
         <v>4</v>
       </c>
@@ -7672,7 +7711,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B30" s="6"/>
       <c r="G30" t="s">
         <v>56</v>
@@ -7681,7 +7720,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B31" s="6">
         <v>5</v>
       </c>
@@ -7698,13 +7737,13 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B32" s="6"/>
       <c r="K32" s="7" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="6">
         <v>6</v>
       </c>
@@ -7718,7 +7757,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="18" t="s">
         <v>73</v>
       </c>
@@ -7728,11 +7767,11 @@
       </c>
       <c r="K34" s="7"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B35" s="6"/>
       <c r="K35" s="7"/>
     </row>
-    <row r="36" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B36" s="11"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
@@ -7762,22 +7801,22 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{722C887D-681D-4D24-BB52-EDFF3D0D1F86}">
   <dimension ref="A1:N80"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" customWidth="1"/>
-    <col min="7" max="7" width="4.140625" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" customWidth="1"/>
+    <col min="3" max="3" width="4.5" customWidth="1"/>
+    <col min="6" max="6" width="9.5" customWidth="1"/>
+    <col min="7" max="7" width="4.1640625" customWidth="1"/>
+    <col min="11" max="11" width="4.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="30"/>
       <c r="B2" s="30"/>
       <c r="D2" s="30"/>
@@ -7796,7 +7835,7 @@
       </c>
       <c r="N2" s="30"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="30" t="s">
         <v>127</v>
       </c>
@@ -7831,7 +7870,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="31">
         <v>37104</v>
       </c>
@@ -7855,7 +7894,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="30"/>
       <c r="B5" s="30"/>
       <c r="D5" s="30"/>
@@ -7868,7 +7907,7 @@
       <c r="M5" s="30"/>
       <c r="N5" s="30"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="30">
         <v>12</v>
       </c>
@@ -7890,7 +7929,7 @@
       <c r="M6" s="30"/>
       <c r="N6" s="30"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="30"/>
       <c r="B7" s="30"/>
       <c r="D7" s="30"/>
@@ -7903,7 +7942,7 @@
       <c r="M7" s="30"/>
       <c r="N7" s="30"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="30">
         <v>15</v>
       </c>
@@ -7920,7 +7959,7 @@
       <c r="M8" s="30"/>
       <c r="N8" s="30"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="30"/>
       <c r="B9" s="30"/>
       <c r="D9" s="30"/>
@@ -7933,7 +7972,7 @@
       <c r="M9" s="30"/>
       <c r="N9" s="30"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="30"/>
       <c r="B10" s="30"/>
       <c r="D10" s="30"/>
@@ -7946,7 +7985,7 @@
       <c r="M10" s="30"/>
       <c r="N10" s="30"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="30">
         <v>21</v>
       </c>
@@ -7968,7 +8007,7 @@
       <c r="M11" s="30"/>
       <c r="N11" s="30"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="30"/>
       <c r="B12" s="30"/>
       <c r="D12" s="30"/>
@@ -7981,7 +8020,7 @@
       <c r="M12" s="30"/>
       <c r="N12" s="30"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="30"/>
       <c r="B13" s="30"/>
       <c r="D13" s="30"/>
@@ -7994,7 +8033,7 @@
       <c r="M13" s="30"/>
       <c r="N13" s="30"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="30"/>
       <c r="B14" s="30"/>
       <c r="D14" s="30"/>
@@ -8007,7 +8046,7 @@
       <c r="M14" s="30"/>
       <c r="N14" s="30"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="30">
         <v>22</v>
       </c>
@@ -8024,7 +8063,7 @@
       <c r="M15" s="30"/>
       <c r="N15" s="30"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="30"/>
       <c r="B16" s="30"/>
       <c r="D16" s="30"/>
@@ -8037,7 +8076,7 @@
       <c r="M16" s="30"/>
       <c r="N16" s="30"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="30">
         <v>28</v>
       </c>
@@ -8054,7 +8093,7 @@
       <c r="M17" s="30"/>
       <c r="N17" s="30"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="30"/>
       <c r="B18" s="30"/>
       <c r="D18" s="30"/>
@@ -8067,12 +8106,12 @@
       <c r="M18" s="30"/>
       <c r="N18" s="30"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="30"/>
       <c r="B22" s="30"/>
       <c r="D22" s="30"/>
@@ -8091,7 +8130,7 @@
       </c>
       <c r="N22" s="30"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="30" t="s">
         <v>127</v>
       </c>
@@ -8126,7 +8165,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="31">
         <v>37104</v>
       </c>
@@ -8150,7 +8189,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="30"/>
       <c r="B25" s="30"/>
       <c r="D25" s="30"/>
@@ -8163,7 +8202,7 @@
       <c r="M25" s="30"/>
       <c r="N25" s="30"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="30">
         <v>12</v>
       </c>
@@ -8185,7 +8224,7 @@
       <c r="M26" s="30"/>
       <c r="N26" s="30"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="30"/>
       <c r="B27" s="30"/>
       <c r="D27" s="30"/>
@@ -8198,7 +8237,7 @@
       <c r="M27" s="30"/>
       <c r="N27" s="30"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="30">
         <v>15</v>
       </c>
@@ -8215,7 +8254,7 @@
       <c r="M28" s="30"/>
       <c r="N28" s="30"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="30"/>
       <c r="B29" s="30"/>
       <c r="D29" s="30"/>
@@ -8228,7 +8267,7 @@
       <c r="M29" s="30"/>
       <c r="N29" s="30"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="30"/>
       <c r="B30" s="30"/>
       <c r="D30" s="30"/>
@@ -8241,7 +8280,7 @@
       <c r="M30" s="30"/>
       <c r="N30" s="30"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="30">
         <v>21</v>
       </c>
@@ -8263,7 +8302,7 @@
       <c r="M31" s="30"/>
       <c r="N31" s="30"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="30"/>
       <c r="B32" s="30"/>
       <c r="D32" s="30"/>
@@ -8276,7 +8315,7 @@
       <c r="M32" s="30"/>
       <c r="N32" s="30"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="30"/>
       <c r="B33" s="30"/>
       <c r="D33" s="30"/>
@@ -8289,7 +8328,7 @@
       <c r="M33" s="30"/>
       <c r="N33" s="30"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="30"/>
       <c r="B34" s="30"/>
       <c r="D34" s="30"/>
@@ -8302,7 +8341,7 @@
       <c r="M34" s="30"/>
       <c r="N34" s="30"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" s="30">
         <v>22</v>
       </c>
@@ -8319,7 +8358,7 @@
       <c r="M35" s="30"/>
       <c r="N35" s="30"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="30"/>
       <c r="B36" s="30"/>
       <c r="D36" s="30"/>
@@ -8332,7 +8371,7 @@
       <c r="M36" s="30"/>
       <c r="N36" s="30"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" s="30">
         <v>28</v>
       </c>
@@ -8349,7 +8388,7 @@
       <c r="M37" s="30"/>
       <c r="N37" s="30"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" s="30"/>
       <c r="B38" s="30"/>
       <c r="D38" s="30"/>
@@ -8362,12 +8401,12 @@
       <c r="M38" s="30"/>
       <c r="N38" s="30"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="30"/>
       <c r="B44" s="30"/>
       <c r="D44" s="30"/>
@@ -8386,7 +8425,7 @@
       </c>
       <c r="N44" s="30"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="30" t="s">
         <v>127</v>
       </c>
@@ -8421,7 +8460,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="31">
         <v>37104</v>
       </c>
@@ -8445,7 +8484,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="30"/>
       <c r="B47" s="30"/>
       <c r="D47" s="30"/>
@@ -8458,7 +8497,7 @@
       <c r="M47" s="30"/>
       <c r="N47" s="30"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="30">
         <v>12</v>
       </c>
@@ -8480,7 +8519,7 @@
       <c r="M48" s="30"/>
       <c r="N48" s="30"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="30"/>
       <c r="B49" s="30"/>
       <c r="D49" s="30"/>
@@ -8493,7 +8532,7 @@
       <c r="M49" s="30"/>
       <c r="N49" s="30"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="30">
         <v>15</v>
       </c>
@@ -8510,7 +8549,7 @@
       <c r="M50" s="30"/>
       <c r="N50" s="30"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="30"/>
       <c r="B51" s="30"/>
       <c r="D51" s="30"/>
@@ -8523,7 +8562,7 @@
       <c r="M51" s="30"/>
       <c r="N51" s="30"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" s="30"/>
       <c r="B52" s="30"/>
       <c r="D52" s="30"/>
@@ -8536,7 +8575,7 @@
       <c r="M52" s="30"/>
       <c r="N52" s="30"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" s="30">
         <v>21</v>
       </c>
@@ -8558,7 +8597,7 @@
       <c r="M53" s="30"/>
       <c r="N53" s="30"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" s="30"/>
       <c r="B54" s="30"/>
       <c r="D54" s="30"/>
@@ -8571,7 +8610,7 @@
       <c r="M54" s="30"/>
       <c r="N54" s="30"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" s="30"/>
       <c r="B55" s="30"/>
       <c r="D55" s="30"/>
@@ -8584,7 +8623,7 @@
       <c r="M55" s="30"/>
       <c r="N55" s="30"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" s="30"/>
       <c r="B56" s="30"/>
       <c r="D56" s="30"/>
@@ -8597,7 +8636,7 @@
       <c r="M56" s="30"/>
       <c r="N56" s="30"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" s="30">
         <v>22</v>
       </c>
@@ -8614,7 +8653,7 @@
       <c r="M57" s="30"/>
       <c r="N57" s="30"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" s="30"/>
       <c r="B58" s="30"/>
       <c r="D58" s="30"/>
@@ -8627,7 +8666,7 @@
       <c r="M58" s="30"/>
       <c r="N58" s="30"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" s="30">
         <v>28</v>
       </c>
@@ -8644,7 +8683,7 @@
       <c r="M59" s="30"/>
       <c r="N59" s="30"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60" s="30"/>
       <c r="B60" s="30"/>
       <c r="D60" s="30"/>
@@ -8657,12 +8696,12 @@
       <c r="M60" s="30"/>
       <c r="N60" s="30"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" s="30"/>
       <c r="B64" s="30"/>
       <c r="D64" s="30"/>
@@ -8681,7 +8720,7 @@
       </c>
       <c r="N64" s="30"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65" s="30" t="s">
         <v>127</v>
       </c>
@@ -8716,7 +8755,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66" s="31">
         <v>37104</v>
       </c>
@@ -8740,7 +8779,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67" s="30"/>
       <c r="B67" s="30"/>
       <c r="D67" s="30"/>
@@ -8753,7 +8792,7 @@
       <c r="M67" s="30"/>
       <c r="N67" s="30"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" s="30">
         <v>12</v>
       </c>
@@ -8775,7 +8814,7 @@
       <c r="M68" s="30"/>
       <c r="N68" s="30"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69" s="30"/>
       <c r="B69" s="30"/>
       <c r="D69" s="30"/>
@@ -8788,7 +8827,7 @@
       <c r="M69" s="30"/>
       <c r="N69" s="30"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70" s="30">
         <v>15</v>
       </c>
@@ -8805,7 +8844,7 @@
       <c r="M70" s="30"/>
       <c r="N70" s="30"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71" s="30"/>
       <c r="B71" s="30"/>
       <c r="D71" s="30"/>
@@ -8818,7 +8857,7 @@
       <c r="M71" s="30"/>
       <c r="N71" s="30"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72" s="30"/>
       <c r="B72" s="30"/>
       <c r="D72" s="30"/>
@@ -8831,7 +8870,7 @@
       <c r="M72" s="30"/>
       <c r="N72" s="30"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73" s="30">
         <v>21</v>
       </c>
@@ -8853,7 +8892,7 @@
       <c r="M73" s="30"/>
       <c r="N73" s="30"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74" s="30"/>
       <c r="B74" s="30"/>
       <c r="D74" s="30"/>
@@ -8866,7 +8905,7 @@
       <c r="M74" s="30"/>
       <c r="N74" s="30"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75" s="30"/>
       <c r="B75" s="30"/>
       <c r="D75" s="30"/>
@@ -8879,7 +8918,7 @@
       <c r="M75" s="30"/>
       <c r="N75" s="30"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76" s="30"/>
       <c r="B76" s="30"/>
       <c r="D76" s="30"/>
@@ -8892,7 +8931,7 @@
       <c r="M76" s="30"/>
       <c r="N76" s="30"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77" s="30">
         <v>22</v>
       </c>
@@ -8909,7 +8948,7 @@
       <c r="M77" s="30"/>
       <c r="N77" s="30"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78" s="30"/>
       <c r="B78" s="30"/>
       <c r="D78" s="30"/>
@@ -8922,7 +8961,7 @@
       <c r="M78" s="30"/>
       <c r="N78" s="30"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79" s="30">
         <v>28</v>
       </c>
@@ -8939,7 +8978,7 @@
       <c r="M79" s="30"/>
       <c r="N79" s="30"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80" s="30"/>
       <c r="B80" s="30"/>
       <c r="D80" s="30"/>
